--- a/output/pdf_financials_xlsx/WMC.xlsx
+++ b/output/pdf_financials_xlsx/WMC.xlsx
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.436787</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001117</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00106</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.250018</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.436787</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001117</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00106</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.250018</v>
       </c>
     </row>
     <row r="37">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/WMC.xlsx
+++ b/output/pdf_financials_xlsx/WMC.xlsx
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.023941</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.0059</v>
+        <v>-0.025957</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.005393</v>
+        <v>0.034211</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.000507</v>
+        <v>0.009816999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -2483,16 +2483,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.108828</v>
+        <v>0.084887</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.01465</v>
+        <v>-0.005407</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.134133</v>
+        <v>0.162951</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.179597</v>
+        <v>0.188907</v>
       </c>
     </row>
     <row r="107">
@@ -3972,7 +3972,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.023941</v>
       </c>
